--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -808,19 +808,37 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9825,0.0028,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.0039,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0685,0.0004,0.0000,0.9705</t>
+    <t>0.9877,0.0019,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.0068,0.0019,0.0000,0.9945</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0309,0.0013,0.0001,0.9863</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0013,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
@@ -829,685 +847,667 @@
     <t>0.9996,0.0002,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9980,0.0017,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0018,0.0004,0.0003</t>
+    <t>0.9860,0.0002,0.0120,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0010,0.9959,0.0012</t>
+  </si>
+  <si>
+    <t>0.0045,0.0005,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0100,0.9877,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0001,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.9768,0.0006,0.0146,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0091,0.0004,0.9886,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.3179,0.6607,0.0026,0.0002</t>
+  </si>
+  <si>
+    <t>0.9795,0.0218,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9992,0.0069</t>
+  </si>
+  <si>
+    <t>0.0018,0.9894,0.0281,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0049,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9846,0.0062,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9803,0.0180,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9968,0.0654,0.0000</t>
+  </si>
+  <si>
+    <t>0.0113,0.0342,0.7517,0.0226</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0176,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.4800,0.0000,0.4456,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0044,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.7896,0.0328,0.7093</t>
+  </si>
+  <si>
+    <t>0.0005,0.9979,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9918,0.5785,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0023,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0166,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.0286,0.0008,0.9695,0.0009</t>
+  </si>
+  <si>
+    <t>0.0059,0.0002,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0041,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0061,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9457,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9982,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8186,0.0013,0.1219,0.0008</t>
+  </si>
+  <si>
+    <t>0.3309,0.0034,0.6224,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9994,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9516,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9466,0.8335,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9721,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0004,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0026,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9536,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.9748,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.7855,0.0697,0.0248</t>
+  </si>
+  <si>
+    <t>0.0001,0.4142,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9847,0.9622,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9608,0.9861,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0013,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0019,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9981,0.0016,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9916,0.0004,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0070,0.0021,0.9881,0.0014</t>
-  </si>
-  <si>
-    <t>0.0010,0.0006,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.9884,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4740,0.0010,0.5973,0.0002</t>
-  </si>
-  <si>
-    <t>0.8128,0.0002,0.2905,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0009,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0148,0.0002,0.9879,0.0002</t>
-  </si>
-  <si>
-    <t>0.0100,0.0005,0.9868,0.0008</t>
+    <t>0.9995,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.6681,0.3162,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9828,0.0072,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0010</t>
-  </si>
-  <si>
-    <t>0.0013,0.9953,0.0089,0.0000</t>
-  </si>
-  <si>
-    <t>0.9947,0.0014,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9814,0.0013,0.0104,0.0003</t>
-  </si>
-  <si>
-    <t>0.7834,0.2651,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.9677,0.2491,0.0001</t>
-  </si>
-  <si>
-    <t>0.0490,0.1587,0.2281,0.0064</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0028,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.1651,0.0000,0.8289,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.2432,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.7008,0.0054,0.9341</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0059,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0011,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0009,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.0016,0.9954,0.0009</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9897,0.0053,0.0034,0.0006</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0290,0.9954,0.0002</t>
-  </si>
-  <si>
-    <t>0.0162,0.0023,0.9798,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0242,0.9840,0.0001,0.0000</t>
+    <t>0.0022,0.0050,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9958,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.9939,0.0021,0.0003</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.8526,0.0002,0.1557,0.0003</t>
-  </si>
-  <si>
-    <t>0.4851,0.0018,0.4901,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9823,0.9144,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8431,0.9784,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0507,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.9469,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0039,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9901,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9854,0.9802,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9747,0.3301,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.3890,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9953,0.8766,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9904,0.4828,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1744,0.8629,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.5782,0.0010,0.4391,0.0002</t>
+  </si>
+  <si>
+    <t>0.4336,0.0001,0.6872,0.0001</t>
+  </si>
+  <si>
+    <t>0.8713,0.0122,0.0329,0.0019</t>
+  </si>
+  <si>
+    <t>0.6618,0.0012,0.2984,0.0021</t>
+  </si>
+  <si>
+    <t>0.0002,0.2144,0.0024,0.9644</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9881,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.7962,0.1293,0.0157,0.0005</t>
+  </si>
+  <si>
+    <t>0.8373,0.1451,0.0071,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.1338,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9242,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0296,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0525,0.0014,0.9629,0.0000</t>
+  </si>
+  <si>
+    <t>0.9953,0.0001,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9316,0.0003,0.0776,0.0001</t>
+  </si>
+  <si>
+    <t>0.1167,0.0000,0.9507,0.0000</t>
+  </si>
+  <si>
+    <t>0.0299,0.0027,0.9775,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0001,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9782,0.9868,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.9883,0.0009,0.0157</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0317,0.9677,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0597,0.0004,0.0003,0.9692</t>
+  </si>
+  <si>
+    <t>0.0005,0.0090,0.9983,0.0026</t>
+  </si>
+  <si>
+    <t>0.5091,0.0000,0.0048,0.3339</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0428,0.9686,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7443,0.0939,0.0511,0.0022</t>
+  </si>
+  <si>
+    <t>0.9683,0.0079,0.0128,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9620,0.0239,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.8631,0.1514,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.2203,0.8578,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9505,0.0361,0.0086,0.0023</t>
+  </si>
+  <si>
+    <t>0.9819,0.0236,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9826,0.0041,0.0056,0.0009</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9807,0.0123,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.0000,0.0081,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9781,0.0045,0.0089,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0498,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0101,0.9892,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0010,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0102,0.0018,0.9850,0.0007</t>
+  </si>
+  <si>
+    <t>0.0332,0.1035,0.7115,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.0055,0.9947,0.0001</t>
+  </si>
+  <si>
+    <t>0.9177,0.0028,0.0651,0.0004</t>
+  </si>
+  <si>
+    <t>0.9713,0.0004,0.0188,0.0006</t>
+  </si>
+  <si>
+    <t>0.3210,0.0174,0.6293,0.0002</t>
+  </si>
+  <si>
+    <t>0.0480,0.9707,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0336,0.9807,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8966,0.1328,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9806,0.0162,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.2498,0.7873,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9663,0.0038,0.0054,0.0005</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0001,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.6630,0.0153,0.3279,0.0006</t>
+  </si>
+  <si>
+    <t>0.7129,0.0052,0.2004,0.0051</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0017,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.1591,0.8217,0.0047</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9896,0.0068,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9946,0.0053,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0014,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9996,0.0004</t>
+  </si>
+  <si>
+    <t>0.2649,0.1085,0.3750,0.0011</t>
+  </si>
+  <si>
+    <t>0.8818,0.0006,0.0700,0.0026</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0234,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.0059,0.0002,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0006,0.9954,0.0006</t>
+  </si>
+  <si>
+    <t>0.9787,0.0002,0.0163,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0000,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9753,0.0423,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.0007,0.9958,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9964,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9972,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6285,0.4168,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.0205,0.0044,0.9636,0.0016</t>
-  </si>
-  <si>
-    <t>0.9893,0.0001,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.7947,0.0030,0.1261,0.0018</t>
-  </si>
-  <si>
-    <t>0.6298,0.0044,0.2745,0.0030</t>
-  </si>
-  <si>
-    <t>0.0003,0.5436,0.0331,0.5157</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9887,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6789,0.3104,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.6269,0.4330,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9964,0.0002,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.4254,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9621,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0098,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0009,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.3889,0.0013,0.5772,0.0013</t>
-  </si>
-  <si>
-    <t>0.0177,0.0001,0.9906,0.0001</t>
-  </si>
-  <si>
-    <t>0.0266,0.0025,0.9770,0.0001</t>
-  </si>
-  <si>
-    <t>0.0430,0.0004,0.0001,0.9898</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9775,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.1988,0.8139,0.0018,0.0131</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0278,0.9703,0.0016,0.0022</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.0000,0.0000,0.9976</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.9995,0.0049</t>
-  </si>
-  <si>
-    <t>0.9262,0.0001,0.0327,0.0042</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.0194,0.9837,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9850,0.0039,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6936,0.2793,0.0081,0.0005</t>
-  </si>
-  <si>
-    <t>0.9791,0.0047,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.7854,0.1508,0.0003,0.0016</t>
-  </si>
-  <si>
-    <t>0.9174,0.1062,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.5089,0.5853,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.5385,0.0301,0.3085,0.0022</t>
-  </si>
-  <si>
-    <t>0.9927,0.0085,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9874,0.0104,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0062,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9838,0.0049,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0542,0.9865,0.0026</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0027,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.4963,0.0038,0.4474,0.0012</t>
-  </si>
-  <si>
-    <t>0.0029,0.0006,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0103,0.9961,0.0005</t>
-  </si>
-  <si>
-    <t>0.0086,0.0259,0.9592,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.0330,0.9841,0.0002</t>
-  </si>
-  <si>
-    <t>0.1787,0.0079,0.8216,0.0002</t>
-  </si>
-  <si>
-    <t>0.9189,0.0028,0.0571,0.0007</t>
-  </si>
-  <si>
-    <t>0.9861,0.0015,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.8847,0.1750,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.9986,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5690,0.5497,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9495,0.0470,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.2204,0.7978,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9937,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9891,0.0003,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.8191,0.0088,0.1572,0.0004</t>
-  </si>
-  <si>
-    <t>0.2656,0.0028,0.7295,0.0020</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9992,0.0007</t>
-  </si>
-  <si>
-    <t>0.0093,0.0013,0.9829,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0157,0.0005,0.9844,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.0018,0.9930,0.0006</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9899,0.0073,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9967,0.0023,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0014,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0015,0.9991,0.0015</t>
-  </si>
-  <si>
-    <t>0.0140,0.0162,0.9681,0.0030</t>
-  </si>
-  <si>
-    <t>0.9460,0.0003,0.0160,0.0057</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.7119,0.6800,0.0006</t>
-  </si>
-  <si>
-    <t>0.0019,0.0008,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.9624,0.0011,0.0232,0.0004</t>
-  </si>
-  <si>
-    <t>0.9781,0.0000,0.0254,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0001,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0048,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9903,0.0127,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0706,0.9898,0.0009</t>
-  </si>
-  <si>
-    <t>0.0009,0.0031,0.9961,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0898,0.0009,0.9097,0.0060</t>
-  </si>
-  <si>
-    <t>0.0093,0.0009,0.9889,0.0005</t>
-  </si>
-  <si>
-    <t>0.0055,0.0000,0.9957,0.0001</t>
-  </si>
-  <si>
-    <t>0.8071,0.0013,0.0002,0.2835</t>
-  </si>
-  <si>
-    <t>0.0019,0.0175,0.0000,0.9980</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0013,0.9988</t>
-  </si>
-  <si>
-    <t>0.9585,0.0043,0.0019,0.0070</t>
+    <t>0.9922,0.0076,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0016,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0245,0.0007,0.9788,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0852,0.9763,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0009,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0246,0.0007,0.9768,0.0028</t>
+  </si>
+  <si>
+    <t>0.0024,0.0067,0.9931,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.9843,0.0010,0.0005,0.0070</t>
+  </si>
+  <si>
+    <t>0.0057,0.0040,0.0000,0.9959</t>
+  </si>
+  <si>
+    <t>0.0031,0.0001,0.0239,0.9966</t>
+  </si>
+  <si>
+    <t>0.9776,0.0007,0.0047,0.0035</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1893,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2187,7 +2187,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2296,7 +2296,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2408,7 +2408,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2450,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2506,7 +2506,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2534,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2856,7 +2856,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2971,7 +2971,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2985,7 +2985,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2999,7 +2999,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3013,7 +3013,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3027,7 +3027,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3041,7 +3041,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3055,7 +3055,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3069,7 +3069,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3094,10 +3094,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3111,7 +3111,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3125,7 +3125,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3139,7 +3139,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>275</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>358</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3472,10 +3472,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3486,10 +3486,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3500,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3517,7 +3517,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3542,10 +3542,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>311</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3629,7 +3629,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
         <v>394</v>
@@ -3895,7 +3895,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>275</v>
+        <v>359</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>416</v>
+        <v>275</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>418</v>
+        <v>359</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4287,7 +4287,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4315,7 +4315,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4329,7 +4329,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4469,7 +4469,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4522,10 +4522,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4553,7 +4553,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4567,7 +4567,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4592,10 +4592,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4620,10 +4620,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4634,10 +4634,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4662,10 +4662,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4679,7 +4679,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4749,7 +4749,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4760,10 +4760,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4833,7 +4833,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>469</v>
+        <v>319</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4970,10 +4970,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>474</v>
+        <v>329</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5026,10 +5026,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>292</v>
+        <v>431</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>329</v>
+        <v>431</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5113,7 +5113,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5127,7 +5127,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>349</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>275</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>318</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5267,7 +5267,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5281,7 +5281,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5295,7 +5295,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>292</v>
+        <v>488</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5421,7 +5421,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
